--- a/Assignment2/exports/TODO_test_design_artifacts.xlsx
+++ b/Assignment2/exports/TODO_test_design_artifacts.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Requirements" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Risk Analysis" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Coverage Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Test Strategies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Test Suites" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Test Cases" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Optimized Test Suite" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Traceability" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="State Transitions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Strategies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Suites" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optimized Test Suite" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Transitions" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,42 +437,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>requirement_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>requirement_text</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>input_fields</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>data_ranges</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>conditions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>expected_results</t>
         </is>
@@ -1027,57 +1039,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>risk_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>requirement_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>risk_description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>risk_category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>likelihood</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>risk_score</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>test_suggestion</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -1761,52 +1773,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>coverage_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>requirement_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>coverage_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>related_techniques</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -5319,7 +5331,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5571,37 +5583,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>coverage_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>requirement_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>coverage_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>technique</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>strategy_reason</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -8471,62 +8483,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>suite_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>suite_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>coverage_ids</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>techniques</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>coverage_types</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>suite_objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>optimization_basis</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>llm_changes</t>
         </is>
@@ -11275,102 +11287,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>test_case_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>suite_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>suite_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>requirement_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>coverage_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>technique</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>precondition</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>test_data</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>steps</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>expected_result</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>risk_score</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>suite_risk_level</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>suite_priority</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>coverage_type</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>automation_candidate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>design_basis</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>llm_reason</t>
         </is>
@@ -23598,15 +23610,15 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -28664,102 +28676,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>test_case_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>suite_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>suite_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>requirement_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>coverage_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>technique</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>precondition</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>test_data</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>steps</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>expected_result</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>risk_score</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>suite_risk_level</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>suite_priority</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>coverage_type</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>automation_candidate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>design_basis</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>llm_reason</t>
         </is>
@@ -45367,52 +45379,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>requirement_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>requirement_text</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>requirement_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>coverage_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>coverage_description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>suite_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>suite_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>test_case_id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>technique</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
@@ -51914,7 +51926,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -54585,72 +54597,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>sequence_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>transition_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>coverage_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>coverage_goal</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>optimization_rule</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>reset_required</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>source_state</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>guard</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>test_data</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>target_state</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>precondition</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>steps</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>expected_result</t>
         </is>
